--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101535</v>
+        <v>101538</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101538</v>
+        <v>101540</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101540</v>
+        <v>101546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101546</v>
+        <v>101549</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Nike Nylander, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101549</v>
+        <v>101566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nike Nylander, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101566</v>
+        <v>101584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 14750-2024 artfynd.xlsx
+++ b/artfynd/A 14750-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299907</v>
       </c>
       <c r="B2" t="n">
-        <v>101586</v>
+        <v>101161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
